--- a/data/Mörel-Filet/investment_decision/Filet_SFH_2005-2014_investment_decision.xlsx
+++ b/data/Mörel-Filet/investment_decision/Filet_SFH_2005-2014_investment_decision.xlsx
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>5.300380025098253</v>
+        <v>4.014787421998332</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>810.955176438271</v>
       </c>
       <c r="F2" t="n">
-        <v>5.337330325482504</v>
+        <v>4.014787421998335</v>
       </c>
       <c r="G2" t="n">
         <v>810.955176438271</v>
       </c>
       <c r="H2" t="n">
-        <v>5.173651920820188</v>
+        <v>4.014787421998332</v>
       </c>
       <c r="I2" t="n">
         <v>810.955176438271</v>
       </c>
       <c r="J2" t="n">
-        <v>5.579369370922703</v>
+        <v>4.014787421998336</v>
       </c>
       <c r="K2" t="n">
         <v>810.955176438271</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>5.300380025098253</v>
+        <v>4.014787421998332</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>810.955176438271</v>
       </c>
       <c r="F3" t="n">
-        <v>5.337330325482504</v>
+        <v>4.014787421998335</v>
       </c>
       <c r="G3" t="n">
         <v>810.955176438271</v>
       </c>
       <c r="H3" t="n">
-        <v>5.173651920820188</v>
+        <v>4.014787421998332</v>
       </c>
       <c r="I3" t="n">
         <v>810.955176438271</v>
       </c>
       <c r="J3" t="n">
-        <v>5.579369370922703</v>
+        <v>4.014787421998336</v>
       </c>
       <c r="K3" t="n">
         <v>810.955176438271</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>5.300380025098253</v>
+        <v>4.014787421998332</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>810.955176438271</v>
       </c>
       <c r="F4" t="n">
-        <v>5.337330325482504</v>
+        <v>4.014787421998335</v>
       </c>
       <c r="G4" t="n">
         <v>810.955176438271</v>
       </c>
       <c r="H4" t="n">
-        <v>5.173651920820188</v>
+        <v>4.014787421998332</v>
       </c>
       <c r="I4" t="n">
         <v>810.955176438271</v>
       </c>
       <c r="J4" t="n">
-        <v>5.579369370922703</v>
+        <v>4.014787421998336</v>
       </c>
       <c r="K4" t="n">
         <v>810.955176438271</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>5.300380025098253</v>
+        <v>4.014787421998332</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>810.955176438271</v>
       </c>
       <c r="F5" t="n">
-        <v>5.337330325482504</v>
+        <v>4.014787421998335</v>
       </c>
       <c r="G5" t="n">
         <v>810.955176438271</v>
       </c>
       <c r="H5" t="n">
-        <v>5.173651920820188</v>
+        <v>4.014787421998332</v>
       </c>
       <c r="I5" t="n">
         <v>810.955176438271</v>
       </c>
       <c r="J5" t="n">
-        <v>5.579369370922703</v>
+        <v>4.014787421998336</v>
       </c>
       <c r="K5" t="n">
         <v>810.955176438271</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>5.300380025098253</v>
+        <v>4.014787421998332</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>810.955176438271</v>
       </c>
       <c r="F6" t="n">
-        <v>5.337330325482504</v>
+        <v>4.014787421998335</v>
       </c>
       <c r="G6" t="n">
         <v>810.955176438271</v>
       </c>
       <c r="H6" t="n">
-        <v>5.173651920820188</v>
+        <v>4.014787421998332</v>
       </c>
       <c r="I6" t="n">
         <v>810.955176438271</v>
       </c>
       <c r="J6" t="n">
-        <v>5.579369370922703</v>
+        <v>4.014787421998336</v>
       </c>
       <c r="K6" t="n">
         <v>810.955176438271</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>1.216432764657406</v>
+        <v>1.630468314606741</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.216432764657406</v>
+        <v>1.630468314606741</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6985171130508888</v>
+        <v>0.9362704237589404</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6985171130508888</v>
+        <v>0.9362704237589404</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>1.216432764657406</v>
+        <v>1.630468314606741</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.216432764657406</v>
+        <v>1.630468314606741</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9033169156459586</v>
+        <v>1.21077765397402</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9033169156459586</v>
+        <v>1.21077765397402</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>1.216432764657406</v>
+        <v>1.630468314606741</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.216432764657406</v>
+        <v>1.630468314606741</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9945230437607322</v>
+        <v>1.333027486689586</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9945230437607322</v>
+        <v>1.333027486689586</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>1.216432764657406</v>
+        <v>1.630468314606741</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.216432764657406</v>
+        <v>1.630468314606741</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.044501622050686</v>
+        <v>1.400017205051712</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1.044501622050686</v>
+        <v>1.400017205051712</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Filet_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Filet_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>1.216432764657406</v>
+        <v>1.630468314606741</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.216432764657406</v>
+        <v>1.630468314606741</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.075532476499789</v>
+        <v>1.441609988824423</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.075532476499789</v>
+        <v>1.441609988824423</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0002743708235294126</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0002743708235294117</v>
+        <v>0.0002414463247058824</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01166076000000003</v>
+        <v>0.03832623367246143</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
         <v>0.195900768</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01166076000000003</v>
+        <v>0.0383262336724614</v>
       </c>
       <c r="G17" t="n">
         <v>0.195900768</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01166076000000003</v>
+        <v>0.03832623367246142</v>
       </c>
       <c r="I17" t="n">
         <v>0.195900768</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01166076000000003</v>
+        <v>0.03832623367246141</v>
       </c>
       <c r="K17" t="n">
         <v>0.195900768</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0583038</v>
+        <v>0.0619174200051725</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>0.195900768</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0583038</v>
+        <v>0.0619174200051725</v>
       </c>
       <c r="G18" t="n">
         <v>0.195900768</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0583038</v>
+        <v>0.05608704000517249</v>
       </c>
       <c r="I18" t="n">
         <v>0.195900768</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0583038</v>
+        <v>0.05608704000517249</v>
       </c>
       <c r="K18" t="n">
         <v>0.195900768</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0583038</v>
+        <v>0.0619174200051725</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.195900768</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0583038</v>
+        <v>0.0619174200051725</v>
       </c>
       <c r="G19" t="n">
         <v>0.195900768</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0583038</v>
+        <v>0.05608704000517249</v>
       </c>
       <c r="I19" t="n">
         <v>0.195900768</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0583038</v>
+        <v>0.05608704000517249</v>
       </c>
       <c r="K19" t="n">
         <v>0.195900768</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.07560180899993375</v>
+        <v>0.06532868831411962</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.195900768</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07560180899993375</v>
+        <v>0.06532868831412118</v>
       </c>
       <c r="G20" t="n">
         <v>0.195900768</v>
       </c>
       <c r="H20" t="n">
-        <v>0.07560180899993375</v>
+        <v>0.06052068387551198</v>
       </c>
       <c r="I20" t="n">
         <v>0.195900768</v>
       </c>
       <c r="J20" t="n">
-        <v>0.07560180899993375</v>
+        <v>0.05949830831411963</v>
       </c>
       <c r="K20" t="n">
         <v>0.195900768</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.02895876899993379</v>
+        <v>0.04173750198140855</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.195900768</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02895876899993379</v>
+        <v>0.04173750198141008</v>
       </c>
       <c r="G21" t="n">
         <v>0.195900768</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02895876899993379</v>
+        <v>0.04275987754280091</v>
       </c>
       <c r="I21" t="n">
         <v>0.195900768</v>
       </c>
       <c r="J21" t="n">
-        <v>0.02895876899993379</v>
+        <v>0.04173750198140855</v>
       </c>
       <c r="K21" t="n">
         <v>0.195900768</v>
@@ -1477,13 +1477,13 @@
         <v>0.195900768</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.00583038</v>
       </c>
       <c r="I28" t="n">
         <v>0.195900768</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.00583038</v>
       </c>
       <c r="K28" t="n">
         <v>0.195900768</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.004303514526444219</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>0.195900768</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.004071789980482982</v>
       </c>
       <c r="G29" t="n">
         <v>0.195900768</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.008607029052888439</v>
       </c>
       <c r="I29" t="n">
         <v>0.195900768</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.009196209051763264</v>
       </c>
       <c r="K29" t="n">
         <v>0.195900768</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.01166076</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.195900768</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.01166075999999845</v>
       </c>
       <c r="G30" t="n">
         <v>0.195900768</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.01646876443860763</v>
       </c>
       <c r="I30" t="n">
         <v>0.195900768</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.01749114</v>
       </c>
       <c r="K30" t="n">
         <v>0.195900768</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.01166076</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.195900768</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.01166075999999845</v>
       </c>
       <c r="G31" t="n">
         <v>0.195900768</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.01063838443860763</v>
       </c>
       <c r="I31" t="n">
         <v>0.195900768</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.01166076</v>
       </c>
       <c r="K31" t="n">
         <v>0.195900768</v>
@@ -2160,7 +2160,7 @@
         <v>46023</v>
       </c>
       <c r="B47" t="n">
-        <v>0.03825986058778717</v>
+        <v>0.07155648889742852</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2174,19 +2174,19 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F47" t="n">
-        <v>0.04785220528638622</v>
+        <v>0.07436921717754426</v>
       </c>
       <c r="G47" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H47" t="n">
-        <v>0.07212984842700031</v>
+        <v>0.07436921717754426</v>
       </c>
       <c r="I47" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="J47" t="n">
-        <v>0.05003840554295613</v>
+        <v>0.07075140999280768</v>
       </c>
       <c r="K47" t="n">
         <v>1.420607304751947</v>
@@ -2197,7 +2197,7 @@
         <v>47849</v>
       </c>
       <c r="B48" t="n">
-        <v>0.03825986058778717</v>
+        <v>0.07155648889742852</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F48" t="n">
-        <v>0.04785220528638622</v>
+        <v>0.07436921717754426</v>
       </c>
       <c r="G48" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H48" t="n">
-        <v>0.07212984842700031</v>
+        <v>0.07436921717754426</v>
       </c>
       <c r="I48" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="J48" t="n">
-        <v>0.05003840554295613</v>
+        <v>0.07075140999280768</v>
       </c>
       <c r="K48" t="n">
         <v>1.420607304751947</v>
@@ -2234,7 +2234,7 @@
         <v>49675</v>
       </c>
       <c r="B49" t="n">
-        <v>0.03825986058778717</v>
+        <v>0.07155648889742852</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2248,19 +2248,19 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F49" t="n">
-        <v>0.04785220528638622</v>
+        <v>0.07436921717754426</v>
       </c>
       <c r="G49" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H49" t="n">
-        <v>0.07212984842700031</v>
+        <v>0.07436921717754426</v>
       </c>
       <c r="I49" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="J49" t="n">
-        <v>0.05003840554295613</v>
+        <v>0.07075140999280768</v>
       </c>
       <c r="K49" t="n">
         <v>1.420607304751947</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1603278772659883</v>
+        <v>0.1666019980434466</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,19 +2359,19 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F52" t="n">
-        <v>0.118958762005648</v>
+        <v>0.1252026396372876</v>
       </c>
       <c r="G52" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3709180400704274</v>
+        <v>0.1170292545851124</v>
       </c>
       <c r="I52" t="n">
         <v>0.3827550034373275</v>
       </c>
       <c r="J52" t="n">
-        <v>0.3888173393396562</v>
+        <v>0.1575410860054067</v>
       </c>
       <c r="K52" t="n">
         <v>0.3827550034373275</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1603278772659883</v>
+        <v>0.1666019980434466</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F53" t="n">
-        <v>0.118958762005648</v>
+        <v>0.1252026396372876</v>
       </c>
       <c r="G53" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3709180400704274</v>
+        <v>0.1170292545851124</v>
       </c>
       <c r="I53" t="n">
         <v>0.5646665744039971</v>
       </c>
       <c r="J53" t="n">
-        <v>0.3888173393396562</v>
+        <v>0.1575410860054067</v>
       </c>
       <c r="K53" t="n">
         <v>0.5646665744039971</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1603278772659884</v>
+        <v>0.1666019980434466</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F54" t="n">
-        <v>0.118958762005648</v>
+        <v>0.1252026396372876</v>
       </c>
       <c r="G54" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3709180400704274</v>
+        <v>0.1170292545851124</v>
       </c>
       <c r="I54" t="n">
         <v>0.6689643561887508</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3888173393396562</v>
+        <v>0.1575410860054067</v>
       </c>
       <c r="K54" t="n">
         <v>0.6689643561887508</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.4131030050135804</v>
+        <v>0.4151146441782341</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4001992565543901</v>
+        <v>0.3980690962441429</v>
       </c>
       <c r="G55" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3999591844098391</v>
+        <v>0.3980690962441427</v>
       </c>
       <c r="I55" t="n">
         <v>0.7360701830158765</v>
       </c>
       <c r="J55" t="n">
-        <v>0.4144686166759358</v>
+        <v>0.4151146441782341</v>
       </c>
       <c r="K55" t="n">
         <v>0.7360701830158765</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.4131030050135804</v>
+        <v>0.4151146441782341</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4001992565543901</v>
+        <v>0.3980690962441429</v>
       </c>
       <c r="G56" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3999591844098391</v>
+        <v>0.3980690962441427</v>
       </c>
       <c r="I56" t="n">
         <v>0.7827180574943501</v>
       </c>
       <c r="J56" t="n">
-        <v>0.4144686166759358</v>
+        <v>0.4151146441782341</v>
       </c>
       <c r="K56" t="n">
         <v>0.7827180574943501</v>
@@ -2715,7 +2715,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.2822296934416011</v>
+        <v>0.1130525359543626</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2729,19 +2729,19 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2811599671379911</v>
+        <v>0.1130309873539956</v>
       </c>
       <c r="G62" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2772338378127934</v>
+        <v>0.1130309873539958</v>
       </c>
       <c r="I62" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="J62" t="n">
-        <v>0.2724763317929945</v>
+        <v>0.1130525359543626</v>
       </c>
       <c r="K62" t="n">
         <v>1.420607304751947</v>
@@ -2752,7 +2752,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.2822296934416011</v>
+        <v>0.1130525359543626</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,19 +2766,19 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2811599671379911</v>
+        <v>0.1130309873539956</v>
       </c>
       <c r="G63" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2772338378127934</v>
+        <v>0.1130309873539958</v>
       </c>
       <c r="I63" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="J63" t="n">
-        <v>0.2724763317929945</v>
+        <v>0.1130525359543626</v>
       </c>
       <c r="K63" t="n">
         <v>1.420607304751947</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.2822296934416011</v>
+        <v>0.1130525359543626</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F64" t="n">
-        <v>0.2811599671379911</v>
+        <v>0.1130309873539956</v>
       </c>
       <c r="G64" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2772338378127934</v>
+        <v>0.1130309873539958</v>
       </c>
       <c r="I64" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="J64" t="n">
-        <v>0.2724763317929945</v>
+        <v>0.1130525359543626</v>
       </c>
       <c r="K64" t="n">
         <v>1.420607304751947</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.1892168358784345</v>
+        <v>0.09471663790834374</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2013055041820899</v>
+        <v>0.1117621858424348</v>
       </c>
       <c r="G65" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2051561293706627</v>
+        <v>0.111762185842435</v>
       </c>
       <c r="I65" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1816970474699516</v>
+        <v>0.0947166379083437</v>
       </c>
       <c r="K65" t="n">
         <v>1.420607304751947</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.2730955242743563</v>
+        <v>0.1542357080987146</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2851841925780116</v>
+        <v>0.171281256032806</v>
       </c>
       <c r="G66" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2890348177665843</v>
+        <v>0.171281256032806</v>
       </c>
       <c r="I66" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="J66" t="n">
-        <v>0.2655757358658734</v>
+        <v>0.1542357080987147</v>
       </c>
       <c r="K66" t="n">
         <v>1.420607304751947</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.04312292853644753</v>
+        <v>1.420607304751947</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.04312292853644753</v>
+        <v>1.420607304751947</v>
       </c>
     </row>
     <row r="73">
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0730338329289784</v>
+        <v>1.420607304751947</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.0730338329289784</v>
+        <v>1.420607304751947</v>
       </c>
     </row>
     <row r="74">
@@ -3182,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.09614759696560224</v>
+        <v>1.420607304751947</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.09614759696560224</v>
+        <v>1.420607304751947</v>
       </c>
     </row>
     <row r="75">
@@ -3219,13 +3219,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1149391222665793</v>
+        <v>1.420607304751947</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.1149391222665793</v>
+        <v>1.420607304751947</v>
       </c>
     </row>
     <row r="76">
@@ -3256,13 +3256,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1307120813552008</v>
+        <v>1.420607304751947</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1307120813552008</v>
+        <v>1.420607304751947</v>
       </c>
     </row>
     <row r="77">
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.2947472028590707</v>
+        <v>0.2790995279477543</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,22 +3284,22 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F77" t="n">
-        <v>0.326778619568887</v>
+        <v>0.3177077066741644</v>
       </c>
       <c r="G77" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H77" t="n">
-        <v>0.05807838073271297</v>
+        <v>0.3258810917263396</v>
       </c>
       <c r="I77" t="n">
-        <v>0.04312292853644753</v>
+        <v>1.420607304751947</v>
       </c>
       <c r="J77" t="n">
-        <v>0.05807838073271297</v>
+        <v>0.2889655188904151</v>
       </c>
       <c r="K77" t="n">
-        <v>0.04312292853644753</v>
+        <v>1.420607304751947</v>
       </c>
     </row>
     <row r="78">
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.2947472028590707</v>
+        <v>0.2790995279477543</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,22 +3321,22 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F78" t="n">
-        <v>0.326778619568887</v>
+        <v>0.3177077066741644</v>
       </c>
       <c r="G78" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H78" t="n">
-        <v>0.05807838073271297</v>
+        <v>0.3258810917263396</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0730338329289784</v>
+        <v>1.420607304751947</v>
       </c>
       <c r="J78" t="n">
-        <v>0.05807838073271297</v>
+        <v>0.2889655188904151</v>
       </c>
       <c r="K78" t="n">
-        <v>0.0730338329289784</v>
+        <v>1.420607304751947</v>
       </c>
     </row>
     <row r="79">
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.2947472028590707</v>
+        <v>0.2790995279477543</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,22 +3358,22 @@
         <v>1.420607304751947</v>
       </c>
       <c r="F79" t="n">
-        <v>0.326778619568887</v>
+        <v>0.3177077066741644</v>
       </c>
       <c r="G79" t="n">
         <v>1.420607304751947</v>
       </c>
       <c r="H79" t="n">
-        <v>0.05807838073271297</v>
+        <v>0.3258810917263396</v>
       </c>
       <c r="I79" t="n">
-        <v>0.09614759696560224</v>
+        <v>1.420607304751947</v>
       </c>
       <c r="J79" t="n">
-        <v>0.05807838073271297</v>
+        <v>0.2889655188904151</v>
       </c>
       <c r="K79" t="n">
-        <v>0.09614759696560224</v>
+        <v>1.420607304751947</v>
       </c>
     </row>
     <row r="80">
@@ -3404,13 +3404,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1149391222665793</v>
+        <v>1.420607304751947</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1149391222665793</v>
+        <v>1.420607304751947</v>
       </c>
     </row>
     <row r="81">
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1307120813552008</v>
+        <v>1.420607304751947</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1307120813552008</v>
+        <v>1.420607304751947</v>
       </c>
     </row>
     <row r="82">
